--- a/data/gravel/Neuhaus Epyon 2025.xlsx
+++ b/data/gravel/Neuhaus Epyon 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778A3CB3-43D2-A24C-98AE-F5BE4D055447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B80DCBB-9259-EB42-872B-3B85DF3593E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41600" yWindow="-21280" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/gravel/Neuhaus Epyon 2025.xlsx
+++ b/data/gravel/Neuhaus Epyon 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B80DCBB-9259-EB42-872B-3B85DF3593E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA24894-A013-424D-A592-82A99F52487A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41600" yWindow="-21280" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33480" yWindow="-21280" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -254,9 +254,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -345,6 +342,12 @@
   </si>
   <si>
     <t>a8:i31</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>https://neuhausmetalworks.com/cdn/shop/files/01_neuhaus_metalworks_set_19.jpg?v=1737067628&amp;width=823</t>
   </si>
 </sst>
 </file>
@@ -708,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -716,7 +719,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -740,7 +743,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -748,7 +756,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -756,28 +764,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -785,7 +793,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" s="1">
         <v>534</v>
@@ -814,7 +822,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1">
         <v>370</v>
@@ -843,7 +851,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1">
         <v>525</v>
@@ -872,7 +880,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C12" s="1">
         <v>460</v>
@@ -901,7 +909,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" s="1">
         <v>74</v>
@@ -930,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="1">
         <v>70</v>
@@ -959,7 +967,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" s="1">
         <v>110</v>
@@ -985,10 +993,10 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="1">
         <v>700</v>
@@ -1017,7 +1025,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="1">
         <v>1009</v>
@@ -1046,7 +1054,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="1">
         <v>425</v>
@@ -1075,7 +1083,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C19" s="1">
         <v>75</v>
@@ -1126,7 +1134,7 @@
         <v>395</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -1423,7 +1431,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1493,7 +1501,7 @@
         <v>42</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -1514,7 +1522,7 @@
         <v>45</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1550,7 +1558,7 @@
         <v>51</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -1597,7 +1605,7 @@
         <v>58</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1641,7 +1649,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Neuhaus Epyon 2025.xlsx
+++ b/data/gravel/Neuhaus Epyon 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA24894-A013-424D-A592-82A99F52487A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976300BE-AA6D-E343-BC71-56946C02479B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-21280" windowWidth="27760" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10440" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>https://neuhausmetalworks.com/cdn/shop/files/01_neuhaus_metalworks_set_19.jpg?v=1737067628&amp;width=823</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Novato, California, USA</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1652,6 +1658,14 @@
         <v>103</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Neuhaus Epyon 2025.xlsx
+++ b/data/gravel/Neuhaus Epyon 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976300BE-AA6D-E343-BC71-56946C02479B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D445B3B-B060-E946-8E20-8A8FB16EFFD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10440" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>Novato, California, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -705,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1504,165 +1522,195 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1">
-        <v>27.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="1">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B61" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B68" s="1">
-        <v>6000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69" s="1">
-        <v>9500</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="1">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>106</v>
       </c>
     </row>
